--- a/output/pdf_financials_xlsx/CYB.xlsx
+++ b/output/pdf_financials_xlsx/CYB.xlsx
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>2.613884</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2.812646</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>2.779248</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.613884</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2.812646</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.779248</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.006497</v>
+        <v>-1.607387</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.8366209999999999</v>
+        <v>-1.976025</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-4.082431</v>
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.028031</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003082</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002576</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.036134</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.047747</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006092</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00583</v>
       </c>
     </row>
     <row r="13">
@@ -1470,22 +1470,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.605534</v>
+        <v>-4.577503</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.141272</v>
+        <v>-5.13819</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.051908</v>
+        <v>-4.054484</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.785014</v>
+        <v>-4.821148</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.44344</v>
+        <v>0.395693</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.824381</v>
+        <v>-1.82499</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.171207</v>
@@ -1494,10 +1494,10 @@
         <v>233.25</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.23016</v>
+        <v>0.224068</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.316204</v>
+        <v>0.310374</v>
       </c>
     </row>
     <row r="28">
@@ -1544,22 +1544,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.984854</v>
+        <v>-2.956823</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.566695</v>
+        <v>-3.563613</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.466667</v>
+        <v>-2.469243</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.214683</v>
+        <v>-3.250817</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.562591</v>
+        <v>0.514844</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.735133</v>
+        <v>-1.735742</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.104759</v>
@@ -1568,10 +1568,10 @@
         <v>233.25</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.23016</v>
+        <v>0.224068</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.316204</v>
+        <v>0.310374</v>
       </c>
     </row>
     <row r="30">
@@ -1581,22 +1581,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-296.5586583963986</v>
+        <v>-293.773652579193</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-426.3214765108693</v>
+        <v>-425.9530898698455</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-133.1439271263802</v>
+        <v>-133.2829725493244</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-114.9972240545688</v>
+        <v>-116.2898273047144</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>60.78680518414073</v>
+        <v>55.62783963523012</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-219.9982756500229</v>
+        <v>-220.0754910276745</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-68.65609774286567</v>
@@ -1605,10 +1605,10 @@
         <v>92.06740162701749</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>90.63915252234868</v>
+        <v>88.24006615996535</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>92.23077820557694</v>
+        <v>90.5302765138257</v>
       </c>
     </row>
     <row r="31">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" s="5" t="n">
@@ -33510,7 +33510,11 @@
           <t>Selling, general and administrative costs</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E429" s="5" t="n">
         <v>2.613884</v>
       </c>
@@ -33640,7 +33644,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
